--- a/public/Test (1).xlsx
+++ b/public/Test (1).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\projects\laravel\financial-assistant-service\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\workspace\Laravel\cyfgs-brocon-financial-assistance\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC83164A-011D-439A-9EAD-825813573BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,20 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>MALE</t>
   </si>
   <si>
-    <t>BUEA</t>
-  </si>
-  <si>
     <t>Student</t>
   </si>
   <si>
-    <t>Peter Jerry</t>
-  </si>
-  <si>
     <t>Lewis Shella</t>
   </si>
   <si>
@@ -45,9 +40,6 @@
     <t>petterson@gmail.com</t>
   </si>
   <si>
-    <t>Buea Town</t>
-  </si>
-  <si>
     <t>Engineer</t>
   </si>
   <si>
@@ -57,22 +49,37 @@
     <t>joe@gmail.com</t>
   </si>
   <si>
-    <t>Yaounde</t>
-  </si>
-  <si>
     <t>Developer</t>
   </si>
   <si>
     <t>lewis@gmail.com</t>
   </si>
   <si>
-    <t>jerry@gmail.com</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Telephone</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Buea</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -126,12 +133,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -350,63 +356,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4">
-        <v>674019243</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4">
         <v>677809232</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>670060071</v>
@@ -415,38 +421,37 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>678934023</v>
       </c>
       <c r="D4" t="s">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1"/>
-    <hyperlink ref="B4" r:id="rId2"/>
-    <hyperlink ref="B1" r:id="rId3"/>
-    <hyperlink ref="B2" r:id="rId4"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Test (1).xlsx
+++ b/public/Test (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\workspace\Laravel\cyfgs-brocon-financial-assistance\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC83164A-011D-439A-9EAD-825813573BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66754A1C-8072-41D0-B45D-009D0981D976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
